--- a/eastel-report-scripts/reports-pipelines/report-generation-mongo/2-Invoice-Recon/2-Invoice-Recon-report-April.xlsx
+++ b/eastel-report-scripts/reports-pipelines/report-generation-mongo/2-Invoice-Recon/2-Invoice-Recon-report-April.xlsx
@@ -83,7 +83,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
@@ -102,7 +102,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,7 +491,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>117413</t>
         </is>
       </c>
       <c r="E2" s="6" t="n"/>
@@ -599,7 +598,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3050.81</t>
+          <t>%Q004.onnet_mou%</t>
         </is>
       </c>
     </row>
@@ -621,7 +620,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>14629.59</t>
+          <t>%Q004.offnet_mou%</t>
         </is>
       </c>
     </row>
@@ -677,7 +676,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>33265189.98</t>
+          <t>%Q006.mou_mbs%</t>
         </is>
       </c>
     </row>
@@ -699,7 +698,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22696932.78</t>
+          <t>%Q007.mou_mbs%</t>
         </is>
       </c>
     </row>
@@ -717,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.109375" customWidth="1" min="1" max="1"/>
@@ -757,6 +756,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>%TABLE:Q011%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -768,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.109375" customWidth="1" min="1" max="1"/>
@@ -809,303 +815,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Bangladesh</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Myanmar</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Nepal</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>United States/Canada</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>Voice MO</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>%TABLE:Q012%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1119,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.109375" customWidth="1" min="1" max="1"/>
@@ -1158,243 +871,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>6988.9</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>8.49</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Data Roaming</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>2128.15</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>%TABLE:Q013%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1426,141 +906,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>Premium and Special Numbers</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
-        <is>
-          <t>1300 Numbers</t>
-        </is>
-      </c>
-      <c r="D2" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>Premium and Special Numbers</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>Info Services - 100</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>88</v>
-      </c>
-      <c r="E3" s="14" t="n">
-        <v>75.90000000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Premium and Special Numbers</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Info Services - 15454</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>15.83</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Premium and Special Numbers</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Info Services - 15300</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>31</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>27.93</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>Premium and Special Numbers</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Info Services - 15404</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Premium and Special Numbers</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Info Services - 15444</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>%TABLE:Q014%</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1613,26 +962,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>SMS</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>Non-Profit A2P SMS MT Bundled</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>Non Profit A2P (22200,22288,22200EASTEL,601170337777)</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="n">
-        <v>4459</v>
-      </c>
-    </row>
-    <row r="4"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>%TABLE:Q015%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
